--- a/WorkBot/refactor-experimental/data/orders/FingerLakes Farms/FingerLakes Farms_Downtown_20260306.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/FingerLakes Farms/FingerLakes Farms_Downtown_20260306.xlsx
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>9.25</v>
       </c>
       <c r="E4" t="n">
-        <v>18.5</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="5">
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>10.25</v>
       </c>
       <c r="E8" t="n">
-        <v>20.5</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="9">
